--- a/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_3.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1754918674_individual_h_3.xlsx
@@ -658,7 +658,7 @@
         <v>0.008409573156748078</v>
       </c>
       <c r="C2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>14501399</v>
+        <v>4683560</v>
       </c>
       <c r="L2" t="n">
-        <v>8755197</v>
+        <v>2687856</v>
       </c>
       <c r="M2" t="n">
-        <v>2123943</v>
+        <v>637805</v>
       </c>
       <c r="N2" t="n">
-        <v>90795</v>
+        <v>22898</v>
       </c>
       <c r="O2" t="n">
-        <v>1260091</v>
+        <v>376760</v>
       </c>
       <c r="P2" t="n">
-        <v>475777</v>
+        <v>144600</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998513460159302</v>
+        <v>0.999847948551178</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9403916001319885</v>
+        <v>0.9026859998703003</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8745043873786926</v>
+        <v>0.8143890500068665</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8479660749435425</v>
+        <v>0.7567493319511414</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3045687973499298</v>
+        <v>0.2302301526069641</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8645902276039124</v>
+        <v>0.7937102913856506</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9265013933181763</v>
+        <v>0.88839191198349</v>
       </c>
       <c r="X2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>19039140</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>14564199</v>
+        <v>4849843</v>
       </c>
       <c r="AG2" t="n">
-        <v>8940980</v>
+        <v>2984316</v>
       </c>
       <c r="AH2" t="n">
-        <v>2402318</v>
+        <v>801097</v>
       </c>
       <c r="AI2" t="n">
-        <v>177308</v>
+        <v>59133</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1377264</v>
+        <v>459291</v>
       </c>
       <c r="AK2" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9567306637763977</v>
+        <v>0.9567072987556458</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9111908674240112</v>
+        <v>0.9112796187400818</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581739068031311</v>
+        <v>0.8579719662666321</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6626627445220947</v>
+        <v>0.6624432802200317</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020290970802307</v>
+        <v>0.9019978642463684</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314221143722534</v>
+        <v>0.9314266443252563</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002015533191987188</v>
       </c>
       <c r="C3" t="n">
-        <v>2079</v>
+        <v>696</v>
       </c>
       <c r="D3" t="n">
-        <v>14501399</v>
+        <v>4683560</v>
       </c>
       <c r="E3" t="n">
-        <v>696239</v>
+        <v>375916</v>
       </c>
       <c r="F3" t="n">
-        <v>6695</v>
+        <v>3473</v>
       </c>
       <c r="G3" t="n">
-        <v>1084</v>
+        <v>572</v>
       </c>
       <c r="H3" t="n">
-        <v>293</v>
+        <v>173</v>
       </c>
       <c r="I3" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="J3" t="n">
-        <v>30206029</v>
+        <v>10068655</v>
       </c>
       <c r="K3" t="n">
-        <v>33120977</v>
+        <v>10846679</v>
       </c>
       <c r="L3" t="n">
-        <v>38166678</v>
+        <v>12524288</v>
       </c>
       <c r="M3" t="n">
-        <v>46066263</v>
+        <v>15276918</v>
       </c>
       <c r="N3" t="n">
-        <v>48772897</v>
+        <v>16250107</v>
       </c>
       <c r="O3" t="n">
-        <v>47523087</v>
+        <v>15808679</v>
       </c>
       <c r="P3" t="n">
-        <v>48630411</v>
+        <v>16204533</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9535484313964844</v>
+        <v>0.9247987270355225</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8911224603652954</v>
+        <v>0.819690465927124</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7582992315292358</v>
+        <v>0.6828272342681885</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3390555083751678</v>
+        <v>0.256318986415863</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8249039053916931</v>
+        <v>0.7396166920661926</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8205230236053467</v>
+        <v>0.7480561137199402</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>14564199</v>
+        <v>4849843</v>
       </c>
       <c r="Z3" t="n">
-        <v>597304</v>
+        <v>199096</v>
       </c>
       <c r="AA3" t="n">
-        <v>25689</v>
+        <v>8579</v>
       </c>
       <c r="AB3" t="n">
-        <v>20409</v>
+        <v>6817</v>
       </c>
       <c r="AC3" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>30208860</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>33381490</v>
+        <v>11132126</v>
       </c>
       <c r="AG3" t="n">
-        <v>38551659</v>
+        <v>12846342</v>
       </c>
       <c r="AH3" t="n">
-        <v>46050051</v>
+        <v>15349322</v>
       </c>
       <c r="AI3" t="n">
-        <v>48889951</v>
+        <v>16296534</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47570852</v>
+        <v>15856699</v>
       </c>
       <c r="AK3" t="n">
-        <v>48628392</v>
+        <v>16209445</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576779007911682</v>
+        <v>0.9576323628425598</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100318551063538</v>
+        <v>0.9100990891456604</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8576858639717102</v>
+        <v>0.8576458692550659</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6621207594871521</v>
+        <v>0.6619316339492798</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016098380088806</v>
+        <v>0.901633083820343</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313610792160034</v>
+        <v>0.9313350915908813</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03183927763983192</v>
       </c>
       <c r="C4" t="n">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="D4" t="n">
-        <v>856461</v>
+        <v>474046</v>
       </c>
       <c r="E4" t="n">
-        <v>8755197</v>
+        <v>2687856</v>
       </c>
       <c r="F4" t="n">
-        <v>203712</v>
+        <v>110100</v>
       </c>
       <c r="G4" t="n">
-        <v>4643</v>
+        <v>3157</v>
       </c>
       <c r="H4" t="n">
-        <v>4507</v>
+        <v>3685</v>
       </c>
       <c r="I4" t="n">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="J4" t="n">
-        <v>2831</v>
+        <v>965</v>
       </c>
       <c r="K4" t="n">
-        <v>919197</v>
+        <v>504911</v>
       </c>
       <c r="L4" t="n">
-        <v>1256413</v>
+        <v>612601</v>
       </c>
       <c r="M4" t="n">
-        <v>380807</v>
+        <v>205017</v>
       </c>
       <c r="N4" t="n">
-        <v>207315</v>
+        <v>76559</v>
       </c>
       <c r="O4" t="n">
-        <v>197352</v>
+        <v>97922</v>
       </c>
       <c r="P4" t="n">
-        <v>37743</v>
+        <v>18166</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999256730079651</v>
+        <v>0.9999240040779114</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9469243288040161</v>
+        <v>0.9136086106300354</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8827351927757263</v>
+        <v>0.8170311450958252</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8006299138069153</v>
+        <v>0.7178903222084045</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3208882212638855</v>
+        <v>0.2425751388072968</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8442809581756592</v>
+        <v>0.7657093405723572</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8702977299690247</v>
+        <v>0.8122066855430603</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>615017</v>
+        <v>204901</v>
       </c>
       <c r="Z4" t="n">
-        <v>8940980</v>
+        <v>2984316</v>
       </c>
       <c r="AA4" t="n">
-        <v>248782</v>
+        <v>83178</v>
       </c>
       <c r="AB4" t="n">
-        <v>16494</v>
+        <v>5500</v>
       </c>
       <c r="AC4" t="n">
-        <v>3432</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>204</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>658684</v>
+        <v>219464</v>
       </c>
       <c r="AG4" t="n">
-        <v>871432</v>
+        <v>290547</v>
       </c>
       <c r="AH4" t="n">
-        <v>397019</v>
+        <v>132613</v>
       </c>
       <c r="AI4" t="n">
-        <v>90261</v>
+        <v>30132</v>
       </c>
       <c r="AJ4" t="n">
-        <v>149587</v>
+        <v>49902</v>
       </c>
       <c r="AK4" t="n">
-        <v>39762</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9572040438652039</v>
+        <v>0.9571695923805237</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106109738349915</v>
+        <v>0.9106889963150024</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8579298257827759</v>
+        <v>0.8578088283538818</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6623916029930115</v>
+        <v>0.6621873378753662</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018194079399109</v>
+        <v>0.9018154144287109</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313915967941284</v>
+        <v>0.9313808679580688</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>40221</v>
+        <v>18912</v>
       </c>
       <c r="E5" t="n">
-        <v>493886</v>
+        <v>213470</v>
       </c>
       <c r="F5" t="n">
-        <v>2123943</v>
+        <v>637805</v>
       </c>
       <c r="G5" t="n">
-        <v>77277</v>
+        <v>23558</v>
       </c>
       <c r="H5" t="n">
-        <v>63424</v>
+        <v>38712</v>
       </c>
       <c r="I5" t="n">
-        <v>2140</v>
+        <v>1588</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>706427</v>
+        <v>380850</v>
       </c>
       <c r="L5" t="n">
-        <v>1069712</v>
+        <v>591255</v>
       </c>
       <c r="M5" t="n">
-        <v>676987</v>
+        <v>296260</v>
       </c>
       <c r="N5" t="n">
-        <v>176993</v>
+        <v>66436</v>
       </c>
       <c r="O5" t="n">
-        <v>267470</v>
+        <v>132639</v>
       </c>
       <c r="P5" t="n">
-        <v>104069</v>
+        <v>48701</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999425411224365</v>
+        <v>0.9999412298202515</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9669910669326782</v>
+        <v>0.9460428357124329</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9527671337127686</v>
+        <v>0.9266656637191772</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9785210490226746</v>
+        <v>0.969464123249054</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9921965003013611</v>
+        <v>0.9912893176078796</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9905616044998169</v>
+        <v>0.9859551191329956</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9971204400062561</v>
+        <v>0.9959267377853394</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>24105</v>
+        <v>8036</v>
       </c>
       <c r="Z5" t="n">
-        <v>255382</v>
+        <v>85188</v>
       </c>
       <c r="AA5" t="n">
-        <v>2402318</v>
+        <v>801097</v>
       </c>
       <c r="AB5" t="n">
-        <v>29836</v>
+        <v>9959</v>
       </c>
       <c r="AC5" t="n">
-        <v>87390</v>
+        <v>29152</v>
       </c>
       <c r="AD5" t="n">
-        <v>1899</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>643627</v>
+        <v>214567</v>
       </c>
       <c r="AG5" t="n">
-        <v>883929</v>
+        <v>294795</v>
       </c>
       <c r="AH5" t="n">
-        <v>398612</v>
+        <v>132968</v>
       </c>
       <c r="AI5" t="n">
-        <v>90480</v>
+        <v>30201</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150297</v>
+        <v>50108</v>
       </c>
       <c r="AK5" t="n">
-        <v>39800</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735560417175293</v>
+        <v>0.9735605120658875</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643567204475403</v>
+        <v>0.9643431901931763</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9838443994522095</v>
+        <v>0.9838218092918396</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963299632072449</v>
+        <v>0.9963247179985046</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9939107298851013</v>
+        <v>0.9939077496528625</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983844757080078</v>
+        <v>0.9983840584754944</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
       <c r="D6" t="n">
-        <v>22418</v>
+        <v>11894</v>
       </c>
       <c r="E6" t="n">
-        <v>59295</v>
+        <v>17284</v>
       </c>
       <c r="F6" t="n">
-        <v>64484</v>
+        <v>27114</v>
       </c>
       <c r="G6" t="n">
-        <v>90795</v>
+        <v>22898</v>
       </c>
       <c r="H6" t="n">
-        <v>29671</v>
+        <v>9612</v>
       </c>
       <c r="I6" t="n">
-        <v>997</v>
+        <v>480</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>19395</v>
+        <v>6471</v>
       </c>
       <c r="Z6" t="n">
-        <v>16067</v>
+        <v>5370</v>
       </c>
       <c r="AA6" t="n">
-        <v>32633</v>
+        <v>10891</v>
       </c>
       <c r="AB6" t="n">
-        <v>177308</v>
+        <v>59133</v>
       </c>
       <c r="AC6" t="n">
-        <v>20942</v>
+        <v>6988</v>
       </c>
       <c r="AD6" t="n">
-        <v>1443</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="D7" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
-        <v>6672</v>
+        <v>5706</v>
       </c>
       <c r="F7" t="n">
-        <v>104182</v>
+        <v>63002</v>
       </c>
       <c r="G7" t="n">
-        <v>122190</v>
+        <v>48022</v>
       </c>
       <c r="H7" t="n">
-        <v>1260091</v>
+        <v>376760</v>
       </c>
       <c r="I7" t="n">
-        <v>34315</v>
+        <v>15857</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>2436</v>
+        <v>812</v>
       </c>
       <c r="AA7" t="n">
-        <v>88925</v>
+        <v>29635</v>
       </c>
       <c r="AB7" t="n">
-        <v>22727</v>
+        <v>7591</v>
       </c>
       <c r="AC7" t="n">
-        <v>1377264</v>
+        <v>459291</v>
       </c>
       <c r="AD7" t="n">
-        <v>36126</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>385</v>
+        <v>128</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="E8" t="n">
-        <v>321</v>
+        <v>225</v>
       </c>
       <c r="F8" t="n">
-        <v>1734</v>
+        <v>1328</v>
       </c>
       <c r="G8" t="n">
-        <v>2121</v>
+        <v>1250</v>
       </c>
       <c r="H8" t="n">
-        <v>99457</v>
+        <v>45740</v>
       </c>
       <c r="I8" t="n">
-        <v>475777</v>
+        <v>144600</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>243</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>990</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>795</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>37688</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>540046</v>
+        <v>180028</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
